--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_311_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_311_R32.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8663</v>
+        <v>6.6447</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6281</v>
+        <v>6.3057</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2382</v>
+        <v>0.339</v>
       </c>
       <c r="G2" t="n">
         <v>1.997</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1013</v>
+        <v>0.8797</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6923</v>
+        <v>0.3699</v>
       </c>
       <c r="U2" t="n">
-        <v>0.409</v>
+        <v>0.5098</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.081</v>
+        <v>1.2943</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4594</v>
+        <v>1.1113</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3785</v>
+        <v>0.183</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7647</v>
+        <v>0.4265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2318</v>
+        <v>1.2328</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5329</v>
+        <v>-0.8063</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3131</v>
+        <v>1.1662</v>
       </c>
       <c r="K3" t="n">
-        <v>1.462</v>
+        <v>1.1294</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8511</v>
+        <v>0.0368</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5484</v>
+        <v>-0.7398</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2303</v>
+        <v>0.1034</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3182</v>
+        <v>-0.8431</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.0154</v>
+        <v>0.6959</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4038</v>
+        <v>0.172</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7853</v>
+        <v>-0.0549</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6185</v>
+        <v>0.2269</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8082</v>
+        <v>-0.2927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.726</v>
+        <v>1.3546</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0822</v>
+        <v>-1.6473</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4265</v>
+        <v>2.7647</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2328</v>
+        <v>0.2318</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8063</v>
+        <v>2.5329</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1662</v>
+        <v>5.3131</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1294</v>
+        <v>1.462</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0368</v>
+        <v>3.8511</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7398</v>
+        <v>-2.5484</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1034</v>
+        <v>-1.2303</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8431</v>
+        <v>-1.3182</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3141</v>
+        <v>1.0302</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4402</v>
+        <v>0.6805</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1261</v>
+        <v>0.3497</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1473</v>
+        <v>-0.4418</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6694</v>
+        <v>-0.9303</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5221</v>
+        <v>0.4885</v>
       </c>
       <c r="G5" t="n">
         <v>-2.3827</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2464</v>
+        <v>0.4591</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8057</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5592</v>
+        <v>0.5256</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4233</v>
+        <v>-1.1538</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2159</v>
+        <v>-1.98</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7925</v>
+        <v>0.8262</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2321</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1191</v>
+        <v>0.1505</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2161</v>
+        <v>0.0198</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9422</v>
+        <v>-1.6892</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3698</v>
+        <v>1.7236</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.312</v>
+        <v>-3.4129</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0501</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0672</v>
+        <v>0.1858</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4244</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3572</v>
+        <v>0.2563</v>
       </c>
       <c r="V7" t="n">
         <v>-3.2166</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0679</v>
+        <v>-1.9163</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7563</v>
+        <v>-1.6383</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3116</v>
+        <v>-0.278</v>
       </c>
       <c r="G8" t="n">
         <v>-2.802</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1937</v>
+        <v>-0.0422</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>-0.1729</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1691</v>
+        <v>-2.0959</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6288</v>
+        <v>-1.2868</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5403</v>
+        <v>-0.8091</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1259</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.029</v>
+        <v>0.1021</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7468</v>
+        <v>-0.4048</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7758</v>
+        <v>0.507</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5186</v>
+        <v>-2.5579</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7814</v>
+        <v>-2.1903</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7373</v>
+        <v>-0.3676</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9723</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5258</v>
+        <v>0.4865</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2284</v>
+        <v>-0.1806</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2974</v>
+        <v>0.6671</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9342</v>
+        <v>-2.7431</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9748</v>
+        <v>-3.5149</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0406</v>
+        <v>0.7718</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4709</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1784</v>
+        <v>0.3695</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9709</v>
+        <v>-0.5109</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1492</v>
+        <v>0.8804</v>
       </c>
       <c r="V11" t="n">
         <v>1.7501</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0706</v>
+        <v>-5.0723</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2699</v>
+        <v>-4.574</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8008</v>
+        <v>-0.4983</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1234</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8597</v>
+        <v>0.1386</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0297</v>
+        <v>-0.3339</v>
       </c>
       <c r="U12" t="n">
-        <v>0.17</v>
+        <v>0.4725</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.5177</v>
+        <v>-10.024</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.113200000000001</v>
+        <v>-5.619400000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.4049</v>
+        <v>-4.404700000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-12.9712</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.3427</v>
+        <v>-5.342700000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-7.6287</v>
@@ -1468,13 +1468,13 @@
         <v>12.7575</v>
       </c>
       <c r="S13" t="n">
-        <v>2.438099999999999</v>
+        <v>3.9318</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.2186</v>
+        <v>-0.7248999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>4.6566</v>
+        <v>4.656700000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3412</v>
+        <v>7.7579</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3923</v>
+        <v>4.8641</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9489</v>
+        <v>2.8938</v>
       </c>
       <c r="G14" t="n">
         <v>3.5604</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0127</v>
+        <v>0.4294</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.963</v>
+        <v>-0.4911</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9757</v>
+        <v>0.9206</v>
       </c>
       <c r="V14" t="n">
         <v>2.1444</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9224</v>
+        <v>6.8153</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1393</v>
+        <v>4.4931</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7831</v>
+        <v>2.3222</v>
       </c>
       <c r="G15" t="n">
         <v>5.1203</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0561</v>
+        <v>-0.1632</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.187</v>
+        <v>-0.8331</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1309</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0.9304</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3328</v>
+        <v>3.3379</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9838</v>
+        <v>1.63</v>
       </c>
       <c r="F16" t="n">
-        <v>1.349</v>
+        <v>1.7079</v>
       </c>
       <c r="G16" t="n">
         <v>0.4971</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0677</v>
+        <v>0.0727</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1142</v>
+        <v>-0.2396</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0466</v>
+        <v>0.3123</v>
       </c>
       <c r="V16" t="n">
         <v>1.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. CABOCLO</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.982</v>
+        <v>1.4974</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1393</v>
+        <v>-1.6118</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1573</v>
+        <v>3.1092</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9327</v>
+        <v>0.5775</v>
       </c>
       <c r="H17" t="n">
-        <v>1.437</v>
+        <v>-1.1992</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4957</v>
+        <v>1.7767</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7367</v>
+        <v>0.1885</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3444</v>
+        <v>-1.3304</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3923</v>
+        <v>1.5189</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.804</v>
+        <v>0.389</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0926</v>
+        <v>0.1313</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8966</v>
+        <v>0.2578</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5021</v>
+        <v>-0.2399</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5975</v>
+        <v>-0.6405</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0953</v>
+        <v>0.4007</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MUSA</t>
+          <t>B. CABOCLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4217</v>
+        <v>1.1057</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1592</v>
+        <v>3.1393</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5809</v>
+        <v>-2.0336</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3547</v>
+        <v>2.9327</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4551</v>
+        <v>1.437</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1004</v>
+        <v>1.4957</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8267</v>
+        <v>3.7367</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4487</v>
+        <v>1.3444</v>
       </c>
       <c r="L18" t="n">
-        <v>0.378</v>
+        <v>2.3923</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.472</v>
+        <v>-0.804</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0063</v>
+        <v>0.0926</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4783</v>
+        <v>-0.8966</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2447</v>
+        <v>-0.3785</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1845</v>
+        <v>-0.5975</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4292</v>
+        <v>0.219</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6778999999999999</v>
+        <v>-2.1444</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>D. MUSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1505</v>
+        <v>0.4058</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0836</v>
+        <v>-1.2771</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2341</v>
+        <v>1.683</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5775</v>
+        <v>1.3547</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1992</v>
+        <v>1.4551</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7767</v>
+        <v>-0.1004</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1885</v>
+        <v>1.8267</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3304</v>
+        <v>1.4487</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5189</v>
+        <v>0.378</v>
       </c>
       <c r="M19" t="n">
-        <v>0.389</v>
+        <v>-0.472</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1313</v>
+        <v>0.0063</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2578</v>
+        <v>-0.4783</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1598</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5867</v>
+        <v>0.2289</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1123</v>
+        <v>-0.3025</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4744</v>
+        <v>0.5313</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1092</v>
+        <v>-0.5366</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6653</v>
+        <v>-1.6089</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5561</v>
+        <v>1.0722</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8058999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6967</v>
+        <v>0.2693</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5351</v>
+        <v>-0.4086</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1617</v>
+        <v>0.6778</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6925</v>
+        <v>-1.7597</v>
       </c>
       <c r="E21" t="n">
         <v>-1.9639</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2714</v>
+        <v>0.2041</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3332</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046</v>
+        <v>0.0373</v>
       </c>
       <c r="T21" t="n">
         <v>-0.5149</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6194</v>
+        <v>0.5522</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7462</v>
+        <v>-1.8299</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.635</v>
+        <v>-0.5171</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1112</v>
+        <v>-1.3129</v>
       </c>
       <c r="G22" t="n">
         <v>0.404</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1502</v>
+        <v>-0.2339</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3725</v>
+        <v>0.1709</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0849</v>
+        <v>-2.9169</v>
       </c>
       <c r="E23" t="n">
         <v>-2.743</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3419</v>
+        <v>-0.1738</v>
       </c>
       <c r="G23" t="n">
         <v>0.6637</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2693</v>
+        <v>-0.1013</v>
       </c>
       <c r="T23" t="n">
         <v>-0.224</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.5178</v>
+        <v>13.8769</v>
       </c>
       <c r="E24" t="n">
-        <v>4.404700000000002</v>
+        <v>4.4047</v>
       </c>
       <c r="F24" t="n">
-        <v>7.1131</v>
+        <v>9.472100000000001</v>
       </c>
       <c r="G24" t="n">
         <v>12.9713</v>
@@ -2302,7 +2302,7 @@
         <v>15.2436</v>
       </c>
       <c r="K24" t="n">
-        <v>5.7421</v>
+        <v>5.742099999999999</v>
       </c>
       <c r="L24" t="n">
         <v>9.5014</v>
@@ -2311,13 +2311,13 @@
         <v>-2.2724</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3996</v>
+        <v>-0.3996000000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-1.8727</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1596</v>
+        <v>-1.159599999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.7576</v>
@@ -2326,13 +2326,13 @@
         <v>11.5979</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.438</v>
+        <v>-0.07920000000000005</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.656700000000001</v>
+        <v>-4.6566</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2185</v>
+        <v>4.5775</v>
       </c>
       <c r="V24" t="n">
         <v>2.144400000000001</v>
